--- a/outputs/40892.xlsx
+++ b/outputs/40892.xlsx
@@ -167,16 +167,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -372,184 +376,184 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A2)),$D$3:$D$7),"")</f>
+      <c r="B2" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A2)),0),1),"")</f>
         <v>Red</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A3)),$D$3:$D$7),"")</f>
+      <c r="B3" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A3)),0),1),"")</f>
         <v>Gold</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A4)),$D$3:$D$7),"")</f>
+      <c r="B4" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A4)),0),1),"")</f>
         <v>Red</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A5)),$D$3:$D$7),"")</f>
+      <c r="B5" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A5)),0),1),"")</f>
         <v>Blue</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A6)),$D$3:$D$7),"")</f>
+      <c r="B6" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A6)),0),1),"")</f>
         <v>Black</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A7)),$D$3:$D$7),"")</f>
+      <c r="B7" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A7)),0),1),"")</f>
         <v>Red</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A8)),$D$3:$D$7),"")</f>
+      <c r="B8" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A8)),0),1),"")</f>
         <v/>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A9)),$D$3:$D$7),"")</f>
+      <c r="B9" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A9)),0),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A10)),$D$3:$D$7),"")</f>
+      <c r="B10" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A10)),0),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A11)),$D$3:$D$7),"")</f>
+      <c r="B11" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A11)),0),1),"")</f>
         <v>Red</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A12)),$D$3:$D$7),"")</f>
+      <c r="B12" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A12)),0),1),"")</f>
         <v>Black</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A13)),$D$3:$D$7),"")</f>
+      <c r="B13" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A13)),0),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A14)),$D$3:$D$7),"")</f>
+      <c r="B14" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A14)),0),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A15)),$D$3:$D$7),"")</f>
+      <c r="B15" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A15)),0),1),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A16)),$D$3:$D$7),"")</f>
+      <c r="B16" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A16)),0),1),"")</f>
         <v>Red</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="0" t="str">
-        <f aca="false">IFERROR(LOOKUP(2,1/ISNUMBER(SEARCH($D$3:$D$7,A17)),$D$3:$D$7),"")</f>
+      <c r="B17" s="1" t="str">
+        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A17)),0),1),"")</f>
         <v>Black</v>
       </c>
     </row>

--- a/outputs/40892.xlsx
+++ b/outputs/40892.xlsx
@@ -397,7 +397,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A2)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A2)),0)),"")</f>
         <v>Red</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -409,7 +409,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A3)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A3)),0)),"")</f>
         <v>Gold</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -421,7 +421,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A4)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A4)),0)),"")</f>
         <v>Red</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -433,8 +433,8 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A5)),0),1),"")</f>
-        <v>Blue</v>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A5)),0)),"")</f>
+        <v/>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
@@ -445,8 +445,8 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A6)),0),1),"")</f>
-        <v>Black</v>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A6)),0)),"")</f>
+        <v/>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -457,7 +457,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A7)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A7)),0)),"")</f>
         <v>Red</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -469,7 +469,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A8)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A8)),0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="1" t="s">
@@ -481,7 +481,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A9)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A9)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -490,7 +490,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A10)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A10)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A11)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A11)),0)),"")</f>
         <v>Red</v>
       </c>
     </row>
@@ -508,8 +508,8 @@
         <v>18</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A12)),0),1),"")</f>
-        <v>Black</v>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A12)),0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -517,7 +517,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A13)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A13)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A14)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A14)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -535,7 +535,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A15)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A15)),0)),"")</f>
         <v/>
       </c>
     </row>
@@ -544,7 +544,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A16)),0),1),"")</f>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A16)),0)),"")</f>
         <v>Red</v>
       </c>
     </row>
@@ -553,8 +553,8 @@
         <v>18</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f aca="false">IFERROR(INDEX($D$3:$D$8,MATCH(TRUE(),ISNUMBER(SEARCH($D$3:$D$8,A17)),0),1),"")</f>
-        <v>Black</v>
+        <f aca="false">IFERROR(INDEX($D$2:$D$4,MATCH(TRUE(),ISNUMBER(SEARCH($D$2:$D$4,A17)),0)),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
